--- a/data/FINANZAS_BRAIN_STUDIO_2026.xlsx
+++ b/data/FINANZAS_BRAIN_STUDIO_2026.xlsx
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M12"/>
+  <dimension ref="A1:M17"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -450,388 +450,593 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Bonsai CTG</v>
+        <v>Gobernación de Bolívar</v>
       </c>
       <c r="B3">
-        <v>2000000</v>
+        <v>6000000</v>
       </c>
       <c r="C3">
-        <v>2000000</v>
+        <v>6000000</v>
       </c>
       <c r="D3">
-        <v>2000000</v>
+        <v>6000000</v>
       </c>
       <c r="E3">
-        <v>2000000</v>
+        <v>6000000</v>
       </c>
       <c r="F3">
-        <v>2000000</v>
+        <v>6000000</v>
       </c>
       <c r="G3">
-        <v>2000000</v>
+        <v>6000000</v>
       </c>
       <c r="H3">
-        <v>2000000</v>
+        <v>6000000</v>
       </c>
       <c r="I3">
-        <v>2000000</v>
+        <v>6000000</v>
       </c>
       <c r="J3">
-        <v>2000000</v>
+        <v>6000000</v>
       </c>
       <c r="K3">
-        <v>2000000</v>
+        <v>6000000</v>
       </c>
       <c r="L3">
-        <v>2000000</v>
+        <v>6000000</v>
       </c>
       <c r="M3">
-        <v>2000000</v>
+        <v>6000000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Muebles Nuva</v>
+        <v>Mio Agencia</v>
       </c>
       <c r="B4">
-        <v>3000000</v>
+        <v>4000000</v>
       </c>
       <c r="C4">
-        <v>3000000</v>
+        <v>4000000</v>
       </c>
       <c r="D4">
-        <v>3000000</v>
+        <v>4000000</v>
       </c>
       <c r="E4">
-        <v>3000000</v>
+        <v>4000000</v>
       </c>
       <c r="F4">
-        <v>3000000</v>
+        <v>4000000</v>
       </c>
       <c r="G4">
-        <v>3000000</v>
+        <v>4000000</v>
       </c>
       <c r="H4">
-        <v>3000000</v>
+        <v>4000000</v>
       </c>
       <c r="I4">
-        <v>3000000</v>
+        <v>4000000</v>
       </c>
       <c r="J4">
-        <v>3000000</v>
+        <v>4000000</v>
       </c>
       <c r="K4">
-        <v>3000000</v>
+        <v>4000000</v>
       </c>
       <c r="L4">
-        <v>3000000</v>
+        <v>4000000</v>
       </c>
       <c r="M4">
-        <v>3000000</v>
+        <v>4000000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>EGRESOS</v>
+        <v>Unimudanzas</v>
+      </c>
+      <c r="B5">
+        <v>3000000</v>
+      </c>
+      <c r="C5">
+        <v>3000000</v>
+      </c>
+      <c r="D5">
+        <v>3000000</v>
+      </c>
+      <c r="E5">
+        <v>3000000</v>
+      </c>
+      <c r="F5">
+        <v>3000000</v>
+      </c>
+      <c r="G5">
+        <v>3000000</v>
+      </c>
+      <c r="H5">
+        <v>3000000</v>
+      </c>
+      <c r="I5">
+        <v>3000000</v>
+      </c>
+      <c r="J5">
+        <v>3000000</v>
+      </c>
+      <c r="K5">
+        <v>3000000</v>
+      </c>
+      <c r="L5">
+        <v>3000000</v>
+      </c>
+      <c r="M5">
+        <v>3000000</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Nómina</v>
+        <v>Grupo Brieva</v>
       </c>
       <c r="B6">
-        <v>12000000</v>
+        <v>3500000</v>
       </c>
       <c r="C6">
-        <v>12000000</v>
+        <v>3500000</v>
       </c>
       <c r="D6">
-        <v>12000000</v>
+        <v>3500000</v>
       </c>
       <c r="E6">
-        <v>12000000</v>
+        <v>3500000</v>
       </c>
       <c r="F6">
-        <v>12000000</v>
+        <v>3500000</v>
       </c>
       <c r="G6">
-        <v>12000000</v>
+        <v>3500000</v>
       </c>
       <c r="H6">
-        <v>12000000</v>
+        <v>3500000</v>
       </c>
       <c r="I6">
-        <v>12000000</v>
+        <v>3500000</v>
       </c>
       <c r="J6">
-        <v>12000000</v>
+        <v>3500000</v>
       </c>
       <c r="K6">
-        <v>12000000</v>
+        <v>3500000</v>
       </c>
       <c r="L6">
-        <v>12000000</v>
+        <v>3500000</v>
       </c>
       <c r="M6">
-        <v>12000000</v>
+        <v>3500000</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Pauta</v>
+        <v>Elvira</v>
       </c>
       <c r="B7">
-        <v>5000000</v>
+        <v>2500000</v>
       </c>
       <c r="C7">
-        <v>5000000</v>
+        <v>2500000</v>
       </c>
       <c r="D7">
-        <v>5000000</v>
+        <v>2500000</v>
       </c>
       <c r="E7">
-        <v>5000000</v>
+        <v>2500000</v>
       </c>
       <c r="F7">
-        <v>5000000</v>
+        <v>2500000</v>
       </c>
       <c r="G7">
-        <v>5000000</v>
+        <v>2500000</v>
       </c>
       <c r="H7">
-        <v>5000000</v>
+        <v>2500000</v>
       </c>
       <c r="I7">
-        <v>5000000</v>
+        <v>2500000</v>
       </c>
       <c r="J7">
-        <v>5000000</v>
+        <v>2500000</v>
       </c>
       <c r="K7">
-        <v>5000000</v>
+        <v>2500000</v>
       </c>
       <c r="L7">
-        <v>5000000</v>
+        <v>2500000</v>
       </c>
       <c r="M7">
-        <v>5000000</v>
+        <v>2500000</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Logística</v>
+        <v>Muebles Nuva</v>
       </c>
       <c r="B8">
-        <v>2000000</v>
+        <v>3000000</v>
       </c>
       <c r="C8">
-        <v>2000000</v>
+        <v>3000000</v>
       </c>
       <c r="D8">
-        <v>2000000</v>
+        <v>3000000</v>
       </c>
       <c r="E8">
-        <v>2000000</v>
+        <v>3000000</v>
       </c>
       <c r="F8">
-        <v>2000000</v>
+        <v>3000000</v>
       </c>
       <c r="G8">
-        <v>2000000</v>
+        <v>3000000</v>
       </c>
       <c r="H8">
-        <v>2000000</v>
+        <v>3000000</v>
       </c>
       <c r="I8">
-        <v>2000000</v>
+        <v>3000000</v>
       </c>
       <c r="J8">
-        <v>2000000</v>
+        <v>3000000</v>
       </c>
       <c r="K8">
-        <v>2000000</v>
+        <v>3000000</v>
       </c>
       <c r="L8">
-        <v>2000000</v>
+        <v>3000000</v>
       </c>
       <c r="M8">
-        <v>2000000</v>
+        <v>3000000</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Administrativo</v>
+        <v>SunPartners</v>
       </c>
       <c r="B9">
-        <v>2500000</v>
+        <v>3000000</v>
       </c>
       <c r="C9">
-        <v>2500000</v>
+        <v>3000000</v>
       </c>
       <c r="D9">
-        <v>2500000</v>
+        <v>3000000</v>
       </c>
       <c r="E9">
-        <v>2500000</v>
+        <v>3000000</v>
       </c>
       <c r="F9">
-        <v>2500000</v>
+        <v>3000000</v>
       </c>
       <c r="G9">
-        <v>2500000</v>
+        <v>3000000</v>
       </c>
       <c r="H9">
-        <v>2500000</v>
+        <v>3000000</v>
       </c>
       <c r="I9">
-        <v>2500000</v>
+        <v>3000000</v>
       </c>
       <c r="J9">
-        <v>2500000</v>
+        <v>3000000</v>
       </c>
       <c r="K9">
-        <v>2500000</v>
+        <v>3000000</v>
       </c>
       <c r="L9">
-        <v>2500000</v>
+        <v>3000000</v>
       </c>
       <c r="M9">
-        <v>2500000</v>
+        <v>3000000</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Impuestos</v>
-      </c>
-      <c r="B10">
-        <v>1500000</v>
-      </c>
-      <c r="C10">
-        <v>1500000</v>
-      </c>
-      <c r="D10">
-        <v>1500000</v>
-      </c>
-      <c r="E10">
-        <v>1500000</v>
-      </c>
-      <c r="F10">
-        <v>1500000</v>
-      </c>
-      <c r="G10">
-        <v>1500000</v>
-      </c>
-      <c r="H10">
-        <v>1500000</v>
-      </c>
-      <c r="I10">
-        <v>1500000</v>
-      </c>
-      <c r="J10">
-        <v>1500000</v>
-      </c>
-      <c r="K10">
-        <v>1500000</v>
-      </c>
-      <c r="L10">
-        <v>1500000</v>
-      </c>
-      <c r="M10">
-        <v>1500000</v>
+        <v>EGRESOS</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Financiero</v>
+        <v>Nómina</v>
       </c>
       <c r="B11">
-        <v>400000</v>
+        <v>12000000</v>
       </c>
       <c r="C11">
-        <v>400000</v>
+        <v>12000000</v>
       </c>
       <c r="D11">
-        <v>400000</v>
+        <v>12000000</v>
       </c>
       <c r="E11">
-        <v>400000</v>
+        <v>12000000</v>
       </c>
       <c r="F11">
-        <v>400000</v>
+        <v>12000000</v>
       </c>
       <c r="G11">
-        <v>400000</v>
+        <v>12000000</v>
       </c>
       <c r="H11">
-        <v>400000</v>
+        <v>12000000</v>
       </c>
       <c r="I11">
-        <v>400000</v>
+        <v>12000000</v>
       </c>
       <c r="J11">
-        <v>400000</v>
+        <v>12000000</v>
       </c>
       <c r="K11">
-        <v>400000</v>
+        <v>12000000</v>
       </c>
       <c r="L11">
-        <v>400000</v>
+        <v>12000000</v>
       </c>
       <c r="M11">
-        <v>400000</v>
+        <v>12000000</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
+        <v>Pauta</v>
+      </c>
+      <c r="B12">
+        <v>5000000</v>
+      </c>
+      <c r="C12">
+        <v>5000000</v>
+      </c>
+      <c r="D12">
+        <v>5000000</v>
+      </c>
+      <c r="E12">
+        <v>5000000</v>
+      </c>
+      <c r="F12">
+        <v>5000000</v>
+      </c>
+      <c r="G12">
+        <v>5000000</v>
+      </c>
+      <c r="H12">
+        <v>5000000</v>
+      </c>
+      <c r="I12">
+        <v>5000000</v>
+      </c>
+      <c r="J12">
+        <v>5000000</v>
+      </c>
+      <c r="K12">
+        <v>5000000</v>
+      </c>
+      <c r="L12">
+        <v>5000000</v>
+      </c>
+      <c r="M12">
+        <v>5000000</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>Logística</v>
+      </c>
+      <c r="B13">
+        <v>2000000</v>
+      </c>
+      <c r="C13">
+        <v>2000000</v>
+      </c>
+      <c r="D13">
+        <v>2000000</v>
+      </c>
+      <c r="E13">
+        <v>2000000</v>
+      </c>
+      <c r="F13">
+        <v>2000000</v>
+      </c>
+      <c r="G13">
+        <v>2000000</v>
+      </c>
+      <c r="H13">
+        <v>2000000</v>
+      </c>
+      <c r="I13">
+        <v>2000000</v>
+      </c>
+      <c r="J13">
+        <v>2000000</v>
+      </c>
+      <c r="K13">
+        <v>2000000</v>
+      </c>
+      <c r="L13">
+        <v>2000000</v>
+      </c>
+      <c r="M13">
+        <v>2000000</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>Administrativo</v>
+      </c>
+      <c r="B14">
+        <v>2500000</v>
+      </c>
+      <c r="C14">
+        <v>2500000</v>
+      </c>
+      <c r="D14">
+        <v>2500000</v>
+      </c>
+      <c r="E14">
+        <v>2500000</v>
+      </c>
+      <c r="F14">
+        <v>2500000</v>
+      </c>
+      <c r="G14">
+        <v>2500000</v>
+      </c>
+      <c r="H14">
+        <v>2500000</v>
+      </c>
+      <c r="I14">
+        <v>2500000</v>
+      </c>
+      <c r="J14">
+        <v>2500000</v>
+      </c>
+      <c r="K14">
+        <v>2500000</v>
+      </c>
+      <c r="L14">
+        <v>2500000</v>
+      </c>
+      <c r="M14">
+        <v>2500000</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>Impuestos</v>
+      </c>
+      <c r="B15">
+        <v>1500000</v>
+      </c>
+      <c r="C15">
+        <v>1500000</v>
+      </c>
+      <c r="D15">
+        <v>1500000</v>
+      </c>
+      <c r="E15">
+        <v>1500000</v>
+      </c>
+      <c r="F15">
+        <v>1500000</v>
+      </c>
+      <c r="G15">
+        <v>1500000</v>
+      </c>
+      <c r="H15">
+        <v>1500000</v>
+      </c>
+      <c r="I15">
+        <v>1500000</v>
+      </c>
+      <c r="J15">
+        <v>1500000</v>
+      </c>
+      <c r="K15">
+        <v>1500000</v>
+      </c>
+      <c r="L15">
+        <v>1500000</v>
+      </c>
+      <c r="M15">
+        <v>1500000</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>Financiero</v>
+      </c>
+      <c r="B16">
+        <v>400000</v>
+      </c>
+      <c r="C16">
+        <v>400000</v>
+      </c>
+      <c r="D16">
+        <v>400000</v>
+      </c>
+      <c r="E16">
+        <v>400000</v>
+      </c>
+      <c r="F16">
+        <v>400000</v>
+      </c>
+      <c r="G16">
+        <v>400000</v>
+      </c>
+      <c r="H16">
+        <v>400000</v>
+      </c>
+      <c r="I16">
+        <v>400000</v>
+      </c>
+      <c r="J16">
+        <v>400000</v>
+      </c>
+      <c r="K16">
+        <v>400000</v>
+      </c>
+      <c r="L16">
+        <v>400000</v>
+      </c>
+      <c r="M16">
+        <v>400000</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
         <v>Operativo</v>
       </c>
-      <c r="B12">
+      <c r="B17">
         <v>1000000</v>
       </c>
-      <c r="C12">
+      <c r="C17">
         <v>1000000</v>
       </c>
-      <c r="D12">
+      <c r="D17">
         <v>1000000</v>
       </c>
-      <c r="E12">
+      <c r="E17">
         <v>1000000</v>
       </c>
-      <c r="F12">
+      <c r="F17">
         <v>1000000</v>
       </c>
-      <c r="G12">
+      <c r="G17">
         <v>1000000</v>
       </c>
-      <c r="H12">
+      <c r="H17">
         <v>1000000</v>
       </c>
-      <c r="I12">
+      <c r="I17">
         <v>1000000</v>
       </c>
-      <c r="J12">
+      <c r="J17">
         <v>1000000</v>
       </c>
-      <c r="K12">
+      <c r="K17">
         <v>1000000</v>
       </c>
-      <c r="L12">
+      <c r="L17">
         <v>1000000</v>
       </c>
-      <c r="M12">
+      <c r="M17">
         <v>1000000</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M12"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M17"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F8"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -861,7 +1066,7 @@
         <v>2026-04-01</v>
       </c>
       <c r="C2">
-        <v>1500000</v>
+        <v>6500000</v>
       </c>
       <c r="D2" t="str">
         <v>2026-04-15</v>
@@ -870,7 +1075,7 @@
         <v>DEBE</v>
       </c>
       <c r="F2" t="str">
-        <v>dijo que pagaba el viernes</v>
+        <v>factura pendiente abril</v>
       </c>
     </row>
     <row r="3">
@@ -881,28 +1086,128 @@
         <v>2026-05-01</v>
       </c>
       <c r="C3">
-        <v>2000000</v>
+        <v>7200000</v>
       </c>
       <c r="D3" t="str">
         <v>2026-05-15</v>
       </c>
       <c r="E3" t="str">
-        <v>PROMESADO</v>
+        <v>DEBE</v>
       </c>
       <c r="F3" t="str">
-        <v>pendiente confirmacion</v>
+        <v>factura pendiente mayo</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>Salsipuedes</v>
+      </c>
+      <c r="B4" t="str">
+        <v>2026-05-01</v>
+      </c>
+      <c r="C4">
+        <v>5400000</v>
+      </c>
+      <c r="D4" t="str">
+        <v>2026-05-15</v>
+      </c>
+      <c r="E4" t="str">
+        <v>DEBE</v>
+      </c>
+      <c r="F4" t="str">
+        <v>cuenta vencida</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>Colegio Las Américas</v>
+      </c>
+      <c r="B5" t="str">
+        <v>2026-05-01</v>
+      </c>
+      <c r="C5">
+        <v>4800000</v>
+      </c>
+      <c r="D5" t="str">
+        <v>2026-05-15</v>
+      </c>
+      <c r="E5" t="str">
+        <v>DEBE</v>
+      </c>
+      <c r="F5" t="str">
+        <v>pendiente cobro</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>Alestructurar</v>
+      </c>
+      <c r="B6" t="str">
+        <v>2026-05-01</v>
+      </c>
+      <c r="C6">
+        <v>5200000</v>
+      </c>
+      <c r="D6" t="str">
+        <v>2026-05-15</v>
+      </c>
+      <c r="E6" t="str">
+        <v>DEBE</v>
+      </c>
+      <c r="F6" t="str">
+        <v>promesa de pago</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>New Pueblito</v>
+      </c>
+      <c r="B7" t="str">
+        <v>2026-05-01</v>
+      </c>
+      <c r="C7">
+        <v>6100000</v>
+      </c>
+      <c r="D7" t="str">
+        <v>2026-05-15</v>
+      </c>
+      <c r="E7" t="str">
+        <v>DEBE</v>
+      </c>
+      <c r="F7" t="str">
+        <v>pendiente transferencia</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>Elvira Utria</v>
+      </c>
+      <c r="B8" t="str">
+        <v>2026-05-01</v>
+      </c>
+      <c r="C8">
+        <v>3555614</v>
+      </c>
+      <c r="D8" t="str">
+        <v>2026-05-15</v>
+      </c>
+      <c r="E8" t="str">
+        <v>DEBE</v>
+      </c>
+      <c r="F8" t="str">
+        <v>saldo conciliado a pagar</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F8"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E10"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -923,13 +1228,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>admin@brainstudio.com</v>
+        <v>francisco.villa@brainstudio.com</v>
       </c>
       <c r="B2">
-        <v>3000000</v>
+        <v>6000000</v>
       </c>
       <c r="C2">
-        <v>400000</v>
+        <v>800000</v>
       </c>
       <c r="D2" t="str">
         <v>2021-01-01</v>
@@ -940,13 +1245,13 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>chrodny@gmail.com</v>
+        <v>claudia@brainstudio.com</v>
       </c>
       <c r="B3">
-        <v>4500000</v>
+        <v>3500000</v>
       </c>
       <c r="C3">
-        <v>550000</v>
+        <v>500000</v>
       </c>
       <c r="D3" t="str">
         <v>2021-01-01</v>
@@ -955,9 +1260,128 @@
         <v/>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>elisa.mestra@brainstudio.com</v>
+      </c>
+      <c r="B4">
+        <v>4000000</v>
+      </c>
+      <c r="C4">
+        <v>550000</v>
+      </c>
+      <c r="D4" t="str">
+        <v>2021-01-01</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>melissa.castano@brainstudio.com</v>
+      </c>
+      <c r="B5">
+        <v>3800000</v>
+      </c>
+      <c r="C5">
+        <v>520000</v>
+      </c>
+      <c r="D5" t="str">
+        <v>2021-01-01</v>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>camila@brainstudio.com</v>
+      </c>
+      <c r="B6">
+        <v>3200000</v>
+      </c>
+      <c r="C6">
+        <v>450000</v>
+      </c>
+      <c r="D6" t="str">
+        <v>2021-01-01</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>jarlan@brainstudio.com</v>
+      </c>
+      <c r="B7">
+        <v>3000000</v>
+      </c>
+      <c r="C7">
+        <v>420000</v>
+      </c>
+      <c r="D7" t="str">
+        <v>2021-01-01</v>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>helen@brainstudio.com</v>
+      </c>
+      <c r="B8">
+        <v>2800000</v>
+      </c>
+      <c r="C8">
+        <v>400000</v>
+      </c>
+      <c r="D8" t="str">
+        <v>2021-01-01</v>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>kamila.del.toro@brainstudio.com</v>
+      </c>
+      <c r="B9">
+        <v>4500000</v>
+      </c>
+      <c r="C9">
+        <v>600000</v>
+      </c>
+      <c r="D9" t="str">
+        <v>2021-01-01</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>practicante@brainstudio.com</v>
+      </c>
+      <c r="B10">
+        <v>1300000</v>
+      </c>
+      <c r="C10">
+        <v>150000</v>
+      </c>
+      <c r="D10" t="str">
+        <v>2021-01-01</v>
+      </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E10"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -985,7 +1409,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>chrodny@gmail.com</v>
+        <v>kamila.del.toro@brainstudio.com</v>
       </c>
       <c r="B2" t="str">
         <v>2026-01-01</v>
@@ -997,12 +1421,12 @@
         <v>500000</v>
       </c>
       <c r="E2" t="str">
-        <v>Bono por desempeño</v>
+        <v>Bono por desempeño extraordinario</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>admin@brainstudio.com</v>
+        <v>francisco.villa@brainstudio.com</v>
       </c>
       <c r="B3" t="str">
         <v>2026-01-01</v>
